--- a/CarBooking.xlsx
+++ b/CarBooking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1211,6 +1211,234 @@
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BK014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>รถไถเดินตาม (ควายเหล็ก) (คห 1011)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>นายสมศักดิ์ ชาวนาไทย</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>แปลงนาข้าว หมู่ 3 สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ไถดะเตรียมดินทำนาปรัง</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ต้องการหัวหมูไถดะ</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BK001</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>รถเกี่ยวนวดข้าว (นข 1234)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>นายมีบุญ ไหม</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>แปลง ป้าหนาย นครสวรรค์</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>นวดข้าว</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BK001</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>รถขุดมันสำปะหลัง (กข 1111)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>นายเอ</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>บางโพ</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ขุดมัน</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BK002</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>รถพ่นยาเพื่อการเกษตร (ญณ 1291)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>นาง สมจุก</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>นครปฐม</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>พ่นยา</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>รออนุมัติ</t>
         </is>
@@ -1227,7 +1455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,6 +1642,210 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>ปป 2233</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>V011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>รถไถเดินตาม (ควายเหล็ก)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>คห 1011</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>V012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>รถคีบอ้อย / รถตักการเกษตร</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ตอ 4455</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>V013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>รถขุดไฮดรอลิกเพื่อการเกษตร (มินิแม็คโครเกษตร)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>มค 7788</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>V014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>รถอีแต๊กเพื่อการเกษตร</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>อต 3344</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>V015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>รถแทรกเตอร์สวนผลไม้ (ทรงแคบ)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>สผ 5566</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>V016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>รถพ่นยาขับเคลื่อน 4 ล้อทรงสูง (High-clearance)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>พส 8899</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>V017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>รถตัดหญ้าเพื่อการเกษตรแบบนั่งขับ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ตห 2244</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>V018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>รถขนส่งผลปาล์มน้ำมันและยางพารา</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ปม 6677</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>V019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>รถหว่านปุ๋ยและปูนโดโลไมต์</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>หป 9911</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>V020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>รถเกลี่ยดินปรับระดับเลเซอร์แปลงนา</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>กด 1221</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>V021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>รถปลูกอ้อยและหยอดปุ๋ย</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ปอ 3322</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>V022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>รถตัดหญ้าอาหารสัตว์และสับหญ้าเนเปียร์</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>สน 7711</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1">
@@ -1865,6 +2297,28 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-20 22:48:33</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>สร้างคำขอจอง</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BK014</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>นายสมศักดิ์ ชาวนาไทย</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CarBooking.xlsx
+++ b/CarBooking.xlsx
@@ -2,17 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17260" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Bookings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Vehicles" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Users" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Users" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Bookings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Vehicles" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Logs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Notifications" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -21,7 +23,7 @@
   <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -52,7 +54,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -415,1032 +417,282 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>รหัสการจอง</t>
+          <t>รหัสผู้ใช้</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>วันที่เริ่มต้น</t>
+          <t>ชื่อ-สกุล</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>เวลาเริ่มต้น</t>
+          <t>รหัสเกษตร/ชื่อผู้ใช้</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>วันที่สิ้นสุด</t>
+          <t>รหัสผ่าน</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>เวลาสิ้นสุด</t>
+          <t>บทบาท</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>ยานพาหนะ</t>
+          <t>อีเมล</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>ผู้ขอใช้รถ</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>สถานที่ปฏิบัติงาน</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>วัตถุประสงค์การใช้งาน</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>หมายเหตุ</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>สถานะ</t>
+          <t>เลขประจำตัวประชาชน</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BK001</t>
+          <t>U001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>นายสมชาย ใจดี</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>100123456789</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>User@123</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>ผู้ใช้</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>รถเกี่ยวนวดข้าว</t>
+          <t>somchai@farm.go.th</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>นาย A</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>พื้นที่ตนเอง</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>เก็บเกี่ยว</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>อนุมัติ</t>
+          <t>1100100111111</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BK002</t>
+          <t>U002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>นางสมศรี สดใส</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>200123456789</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>Farm#123</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>ผู้ใช้</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>รถเกี่ยวอ้อย</t>
+          <t>somsri@farm.go.th</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>นาย B</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>พื้นที่ตนเอง</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>เก็บเกี่ยว</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>อนุมัติ</t>
+          <t>3100500123458</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BK003</t>
+          <t>U003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>ผู้ดูแลระบบ (Admin)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>Admin@123</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>ผู้อนุมัติ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>รถขุดมันสำปะหลัง</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>นาย C</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>ระยอง</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>เก็บเกี่ยว</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>ไม่อนุมัติ</t>
+          <t>admin@agricar.com</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BK004</t>
+          <t>U004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>นายสุวิทย์ การเกษตร</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>150099887766</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>SuwitPass123</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>ผู้ใช้</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>รถพ่นยาเพื่อการเกษตร</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>นาย S</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>นครนายก</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>พ่นยาฆ่าแมลง</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>อนุมัติ</t>
+          <t>suwit_test@farm.co.th</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BK005</t>
+          <t>U005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>นายสมบูรณ์ พูนสุข</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>190088776655</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>Pass12345678</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>ผู้ใช้</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>รถพ่นยาเพื่อการเกษตร</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>นาง W</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>ชลบุรี</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>พ่นยา</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>ไม่อนุมัติ</t>
+          <t>somboon_test@farm.co.th</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BK006</t>
+          <t>U004</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>นางแบบ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>111111111111</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>123456789012</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>ผู้ใช้</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>รถพ่นยาเพื่อการเกษตร</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>สามารถ</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>บางนา</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>พ่นยา</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>อนุมัติ</t>
+          <t>68040686@kmitl.ac.th</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BK007</t>
+          <t>U007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>นางบี</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>nanana</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>hahaha555!</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>ผู้ใช้</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>รถเกี่ยวนวดข้าว</t>
+          <t>nanana@gmail.com</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>นายสมชาย ใจดี</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>บางนา</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>ตรวจแปลงข้าว</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>เตรียมอุปกรณ์เกี่ยวข้าว</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>รออนุมัติ</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>BK008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>รถบรรทุกผลผลิตการเกษตร</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ป้าเล็ก</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>บางโพ</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>ขนของ</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>รออนุมัติ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>BK009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>รถเกี่ยวนวดข้าว</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>นาย สมรชัย</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>นครนายก</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>เกี่ยวข้าว</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>รออนุมัติ</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>BK010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-11-15</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>รถอีแต๋นเพื่อการเกษตร</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ชาวนา สมหวัง</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>แปลงนาข้าว บางเลน</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>ขนย้ายปุ๋ยอินทรีย์</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ต้องการใช้งาน 2 วันเต็ม</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>รออนุมัติ</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>BK011</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-11-15</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>รถบรรทุกผลผลิตการเกษตร</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>จูน</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>นครนายก</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>ขนฟาง</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>รออนุมัติ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>BK012</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>รถแทรกเตอร์เพื่อการเกษตร (ษ 8678)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ทดสอบ ระบบ</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>แปลงทดสอบที่ 1</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ทดสอบการทำงานระบบจอง</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>ทดสอบ</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>รออนุมัติ</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>BK013</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>รถแทรกเตอร์เพื่อการเกษตร (ษ 8678)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ทดสอบ ระบบ</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>แปลงทดสอบที่ 1</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>ทดสอบการทำงานระบบจอง</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>ทดสอบ</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>รออนุมัติ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>BK014</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>รถไถเดินตาม (ควายเหล็ก) (คห 1011)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>นายสมศักดิ์ ชาวนาไทย</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>แปลงนาข้าว หมู่ 3 สุพรรณบุรี</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>ไถดะเตรียมดินทำนาปรัง</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>ต้องการหัวหมูไถดะ</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>รออนุมัติ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>BK001</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>รถเกี่ยวนวดข้าว (นข 1234)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>นายมีบุญ ไหม</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>แปลง ป้าหนาย นครสวรรค์</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>นวดข้าว</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>รออนุมัติ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>BK001</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>รถขุดมันสำปะหลัง (กข 1111)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>นายเอ</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>บางโพ</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>ขุดมัน</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>รออนุมัติ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>BK002</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>รถพ่นยาเพื่อการเกษตร (ญณ 1291)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>นาง สมจุก</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>นครปฐม</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>พ่นยา</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>รออนุมัติ</t>
+          <t>1102345678990</t>
         </is>
       </c>
     </row>
@@ -1455,397 +707,1602 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>รหัสยานพาหนะ</t>
+          <t>รหัสการจอง</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>ประเภทยานพาหนะ</t>
+          <t>วันที่เริ่มต้น</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>ทะเบียน</t>
+          <t>เวลาเริ่มต้น</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>วันที่สิ้นสุด</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>เวลาสิ้นสุด</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ยานพาหนะ</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ผู้ขอใช้รถ</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>สถานที่ปฏิบัติงาน</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>วัตถุประสงค์การใช้งาน</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>หมายเหตุ</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>สถานะ</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V001</t>
+          <t>BK001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>รถแทรกเตอร์เพื่อการเกษตร</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ษ 8678</t>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>รถเกี่ยวนวดข้าว</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>นาย A</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>พื้นที่ตนเอง</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>เก็บเกี่ยว</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>อนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V002</t>
+          <t>BK002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>รถเกี่ยวนวดข้าว</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>นข 1234</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>รถเกี่ยวอ้อย</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>นาย B</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>พื้นที่ตนเอง</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>เก็บเกี่ยว</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>อนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V003</t>
+          <t>BK003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>รถดำนา</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ฟข 8765</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>รถขุดมันสำปะหลัง</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>นาย C</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ระยอง</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>เก็บเกี่ยว</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ไม่อนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V004</t>
+          <t>BK004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>รถเกี่ยวอ้อย</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>นข 5678</t>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>รถพ่นยาเพื่อการเกษตร</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>นาย S</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>นครนายก</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>พ่นยาฆ่าแมลง</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>อนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V005</t>
+          <t>BK005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>รถขุดมันสำปะหลัง</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>กข 1111</t>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>รถพ่นยาเพื่อการเกษตร</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>นาง W</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ชลบุรี</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>พ่นยา</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ไม่อนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V006</t>
+          <t>BK006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>รถพ่นยาเพื่อการเกษตร</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ญณ 1291</t>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>สามารถ</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>บางนา</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>พ่นยา</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>อนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V007</t>
+          <t>BK007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>รถอีแต๋นเพื่อการเกษตร</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ตถ 9876</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>รถเกี่ยวนวดข้าว</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>บางนา</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ตรวจแปลงข้าว</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>เตรียมอุปกรณ์เกี่ยวข้าว</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V008</t>
+          <t>BK008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>รถอัดฟางก้อน</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>อฟ 3456</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>รถบรรทุกผลผลิตการเกษตร</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ป้าเล็ก</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>บางโพ</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ขนของ</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V009</t>
+          <t>BK009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>รถหยอดเมล็ดพันธุ์</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>มพ 7890</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>รถเกี่ยวนวดข้าว</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>นาย สมรชัย</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>นครนายก</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>เกี่ยวข้าว</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V010</t>
+          <t>BK010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>รถบรรทุกผลผลิตการเกษตร</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ปป 2233</t>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>รถอีแต๋นเพื่อการเกษตร</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ชาวนา สมหวัง</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>แปลงนาข้าว บางเลน</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ขนย้ายปุ๋ยอินทรีย์</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ต้องการใช้งาน 2 วันเต็ม</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V011</t>
+          <t>BK011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>รถไถเดินตาม (ควายเหล็ก)</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>คห 1011</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>รถบรรทุกผลผลิตการเกษตร</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>จูน</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>นครนายก</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ขนฟาง</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>อนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V012</t>
+          <t>BK012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>รถคีบอ้อย / รถตักการเกษตร</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ตอ 4455</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>รถแทรกเตอร์เพื่อการเกษตร (ษ 8678)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ทดสอบ ระบบ</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>แปลงทดสอบที่ 1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ทดสอบการทำงานระบบจอง</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ทดสอบ</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ไม่อนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V013</t>
+          <t>BK013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>รถขุดไฮดรอลิกเพื่อการเกษตร (มินิแม็คโครเกษตร)</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>มค 7788</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>รถแทรกเตอร์เพื่อการเกษตร (ษ 8678)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ทดสอบ ระบบ</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>แปลงทดสอบที่ 1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ทดสอบการทำงานระบบจอง</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ทดสอบ</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V014</t>
+          <t>BK014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>รถอีแต๊กเพื่อการเกษตร</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>อต 3344</t>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>รถไถเดินตาม (ควายเหล็ก) (คห 1011)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>นายสมศักดิ์ ชาวนาไทย</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>แปลงนาข้าว หมู่ 3 สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ไถดะเตรียมดินทำนาปรัง</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ต้องการหัวหมูไถดะ</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V015</t>
+          <t>BK001</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>รถแทรกเตอร์สวนผลไม้ (ทรงแคบ)</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>สผ 5566</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>รถเกี่ยวนวดข้าว (นข 1234)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>นายมีบุญ ไหม</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>แปลง ป้าหนาย นครสวรรค์</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>นวดข้าว</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V016</t>
+          <t>BK001</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>รถพ่นยาขับเคลื่อน 4 ล้อทรงสูง (High-clearance)</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>พส 8899</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>รถขุดมันสำปะหลัง (กข 1111)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>นายเอ</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>บางโพ</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ขุดมัน</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V017</t>
+          <t>BK002</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>รถตัดหญ้าเพื่อการเกษตรแบบนั่งขับ</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ตห 2244</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>รถพ่นยาเพื่อการเกษตร (ญณ 1291)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>นาง สมจุก</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>นครปฐม</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>พ่นยา</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V018</t>
+          <t>BK018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>รถขนส่งผลปาล์มน้ำมันและยางพารา</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ปม 6677</t>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>รถแทรกเตอร์เพื่อการเกษตร (ษ 8678)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>แปลงนาทดสอบ อู่ทอง</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>เตรียมดินไถดะ</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V019</t>
+          <t>BK019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>รถหว่านปุ๋ยและปูนโดโลไมต์</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>หป 9911</t>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>รถขุดมันสำปะหลัง (กข 1111)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ไร่มันสำปะหลัง กาญจนบุรี</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ขุดหัวมันสำปะหลัง</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V020</t>
+          <t>BK020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>รถเกลี่ยดินปรับระดับเลเซอร์แปลงนา</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>กด 1221</t>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>รถแทรกเตอร์ 4 ล้อ (ฟอร์ด/คูโบต้า) (กข 1234)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ผ่านฉลุย</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>แปลงทดสอบ</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ทดสอบจอง 4 วัน</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V021</t>
+          <t>BK011</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>รถปลูกอ้อยและหยอดปุ๋ย</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ปอ 3322</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>รถแทรกเตอร์การเกษตร (ฟห 1234)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>แปลงนา หมู่ 3 ต.เกษตรพัฒนา</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>เตรียมแปลงเพาะปลูกข้าวหอมมะลิ</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ต้องการใช้งานด่วน</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V022</t>
+          <t>BK012</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>รถตัดหญ้าอาหารสัตว์และสับหญ้าเนเปียร์</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>สน 7711</t>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>รถเกี่ยวนวดข้าว (นข 1234)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>นางสมศรี สดใส</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ทุ่งรวงทอง แปลง 5</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>เกี่ยวนวดข้าวเหนียว กข6</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BK013</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>รถตัดหญ้าเพื่อการเกษตรแบบนั่งขับ (ตห 2244)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>นางบี</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>แม่ฮ่องสอน</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ตัดหญ้า</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BK014</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>รถแทรกเตอร์ คูโบต้า 50 แรงม้า</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>แปลงนา</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ไถนา</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BK015</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>รถหยอดเมล็ดพันธุ์ (มพ 7890)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>นางบี</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>แปลงนาข้าว</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ปลูกเมล็ดข้าว</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BK026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2099-01-01</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2099-01-01</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>รถแทรกเตอร์คูโบต้า L5018</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>นายสมเกียรติ สุขเกษม</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>แปลงทดสอบ</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ทดสอบระบบ</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BK016</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>รถคีบอ้อย / รถตักการเกษตร (ตอ 4455)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>นางสมศรี สดใส</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>นาบางพลี</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>คีบอ้อย</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>อนุมัติ</t>
         </is>
       </c>
     </row>
@@ -1860,74 +2317,397 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>รหัสผู้ใช้</t>
+          <t>รหัสยานพาหนะ</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>ชื่อ-สกุล</t>
+          <t>ประเภทยานพาหนะ</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>บทบาท</t>
+          <t>ทะเบียน</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>U001</t>
+          <t>V001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>นาย A</t>
+          <t>รถแทรกเตอร์เพื่อการเกษตร</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ผู้ใช้</t>
+          <t>ษ 8678</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>U002</t>
+          <t>V002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>นาย B</t>
+          <t>รถเกี่ยวนวดข้าว</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ผู้ใช้</t>
+          <t>นข 1234</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>U003</t>
+          <t>V003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>รถดำนา</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ผู้อนุมัติ</t>
+          <t>ฟข 8765</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>V004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>รถเกี่ยวอ้อย</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>นข 5678</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>V005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>รถขุดมันสำปะหลัง</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>กข 1111</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>V006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>รถพ่นยาเพื่อการเกษตร</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ญณ 1291</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>V007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>รถอีแต๋นเพื่อการเกษตร</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ตถ 9876</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>V008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>รถอัดฟางก้อน</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>อฟ 3456</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>V009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>รถหยอดเมล็ดพันธุ์</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>มพ 7890</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>V010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>รถบรรทุกผลผลิตการเกษตร</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ปป 2233</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>V011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>รถไถเดินตาม (ควายเหล็ก)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>คห 1011</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>V012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>รถคีบอ้อย / รถตักการเกษตร</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ตอ 4455</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>V013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>รถขุดไฮดรอลิกเพื่อการเกษตร (มินิแม็คโครเกษตร)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>มค 7788</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>V014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>รถอีแต๊กเพื่อการเกษตร</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>อต 3344</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>V015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>รถแทรกเตอร์สวนผลไม้ (ทรงแคบ)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>สผ 5566</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>V016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>รถพ่นยาขับเคลื่อน 4 ล้อทรงสูง (High-clearance)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>พส 8899</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>V017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>รถตัดหญ้าเพื่อการเกษตรแบบนั่งขับ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ตห 2244</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>V018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>รถขนส่งผลปาล์มน้ำมันและยางพารา</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ปม 6677</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>V019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>รถหว่านปุ๋ยและปูนโดโลไมต์</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>หป 9911</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>V020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>รถเกลี่ยดินปรับระดับเลเซอร์แปลงนา</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>กด 1221</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>V021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>รถปลูกอ้อยและหยอดปุ๋ย</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ปอ 3322</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>V022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>รถตัดหญ้าอาหารสัตว์และสับหญ้าเนเปียร์</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>สน 7711</t>
         </is>
       </c>
     </row>
@@ -1942,8 +2722,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <dimension ref="A1:D95"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2316,6 +3096,2700 @@
       <c r="D17" t="inlineStr">
         <is>
           <t>นายสมศักดิ์ ชาวนาไทย</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:23:57</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>user01</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:24:56</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>user01</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:24:56</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบแอดมิน</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ผู้ดูแลระบบ (Admin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:25:39</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>user01</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:25:39</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบแอดมิน</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ผู้ดูแลระบบ (Admin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:25:40</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ส่งออกรายงาน Excel</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Agricarbook_Report_2026-01-01_2026-12-31.xlsx</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ผู้ดูแลระบบ (Admin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:25:40</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>เพิ่มยานพาหนะ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>V999: โดรนเกษตรอัจฉริยะระบบ AI (ดร 9999)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ผู้ดูแลระบบ (Admin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:25:40</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ลบยานพาหนะ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>V999</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ผู้ดูแลระบบ (Admin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:50:51</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:50:51</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>100123456789</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:50:51</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบแอดมิน</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>admin@agricar.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ผู้ดูแลระบบ (Admin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:50:51</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบแอดมิน</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ผู้ดูแลระบบ (Admin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:50:51</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>สมัครสมาชิกใหม่</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>U004 (suwit_test@farm.co.th / 150099887766)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>นายสุวิทย์ การเกษตร</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:50:51</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>suwit_test@farm.co.th</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>นายสุวิทย์ การเกษตร</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:51:10</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>สร้างคำขอจอง</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BK018</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:51:28</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:51:28</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>100123456789</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:51:28</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบแอดมิน</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>admin@agricar.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ผู้ดูแลระบบ (Admin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:51:28</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบแอดมิน</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ผู้ดูแลระบบ (Admin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:51:28</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>สมัครสมาชิกใหม่</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>U005 (somboon_test@farm.co.th / 190088776655)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>นายสมบูรณ์ พูนสุข</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:51:28</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>somboon_test@farm.co.th</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>นายสมบูรณ์ พูนสุข</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:51:28</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>สร้างคำขอจอง</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BK019</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:02:06</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:02:13</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:02:27</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:02:27</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>100123456789</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:02:27</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบแอดมิน</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>admin@agricar.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ผู้ดูแลระบบ (Admin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:02:27</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>สร้างคำขอจอง</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BK020</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ผ่านฉลุย</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:38:25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>สมัครสมาชิกใหม่</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>U007 (CID: 3100500123458 / เมล: tester99@agri.co.th / เกษตร: 310050012345)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ระบบยืนยัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:40:18</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>สมัครสมาชิกใหม่</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>U008 (CID: 1100100111111 / เมล: somkiat.smartfarm@agri.co.th / เกษตร: 778899001122)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>นายสมเกียรติ สมาร์ทฟาร์ม</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:40:18</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>somkiat.smartfarm@agri.co.th</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>นายสมเกียรติ สมาร์ทฟาร์ม</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:40:18</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>778899001122</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>นายสมเกียรติ สมาร์ทฟาร์ม</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:40:18</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1100100111111</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>นายสมเกียรติ สมาร์ทฟาร์ม</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:49:57</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบแอดมิน</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ผู้ดูแลระบบ (Admin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:49:57</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:50:41</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>สมัครสมาชิกใหม่</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>U009 (CID: 1234567890121 / เมล: fresh_user@agri.co.th / เกษตร: 123456789012)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>นายสุรชัย ชาวไร่</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:50:41</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>fresh_user@agri.co.th</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>นายสุรชัย ชาวไร่</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:50:49</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบแอดมิน</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ผู้ดูแลระบบ (Admin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:50:49</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:50:49</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>somsri@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>นางสมศรี สดใส</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00:08</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00:26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00:26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1-1001-00111-11-1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00:26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>3-1005-00123-45-8</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>นางสมศรี สดใส</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00:26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบแอดมิน</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>admin@agricar.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ผู้ดูแลระบบ (Admin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00:27</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>สมัครสมาชิกใหม่</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>U007 (CID: 1100200123456 / เมล: newfarmer2026@farm.go.th)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>นายทดสอบ บัญชีใหม่</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00:35</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00:35</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1-1001-00111-11-1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00:35</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบแอดมิน</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>admin@agricar.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ผู้ดูแลระบบ (Admin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00:35</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>สมัครสมาชิกใหม่</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>U008 (CID: 1100300123458 / เมล: autotest@farm.go.th)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>นายทดสอบ อัตโนมัติ</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:12:42</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>พยายามยกเลิกรายการจองของผู้อื่น</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>BK803 โดย นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:12:43</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>พยายามแก้ไขรายการจองของผู้อื่น</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>BK803 โดย นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:12:43</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ยกเลิกคำขอจอง</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>BK801 (รถแทรกเตอร์ คูโบต้า 50 แรงม้า) เหตุผล: ไม่ไป</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:12:57</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ยกเลิกคำขอจอง</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BK801 (รถแทรกเตอร์ คูโบต้า 50 แรงม้า) เหตุผล: ฝนตกหนัก น้ำท่วมแปลงนาไม่สามารถลงแปลงได้</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:13:19</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>พยายามยกเลิกรายการจองของผู้อื่น</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>BK803 โดย นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:13:19</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>พยายามแก้ไขรายการจองของผู้อื่น</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BK803 โดย นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:13:19</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ยกเลิกคำขอจอง</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>BK801 (รถแทรกเตอร์ คูโบต้า 50 แรงม้า) เหตุผล: ไม่ไป</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:13:27</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ยกเลิกคำขอจอง</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>BK801 (รถแทรกเตอร์ คูโบต้า 50 แรงม้า) เหตุผล: ไม่ไป</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:13:27</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ยกเลิกคำขอจอง</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BK801 (รถแทรกเตอร์ คูโบต้า 50 แรงม้า) เหตุผล: ฝนตกหนัก น้ำท่วมแปลงนาไม่สามารถลงแปลงได้</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:13:44</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>พยายามยกเลิกรายการจองของผู้อื่น</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>BK803 โดย นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:13:44</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>พยายามแก้ไขรายการจองของผู้อื่น</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>BK803 โดย นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:13:44</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ยกเลิกคำขอจอง</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BK801 (รถแทรกเตอร์ คูโบต้า 50 แรงม้า) เหตุผล: ไม่ไป</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:14:32</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>พยายามยกเลิกรายการจองของผู้อื่น</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>BK803 โดย นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:14:32</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>พยายามแก้ไขรายการจองของผู้อื่น</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BK803 โดย นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:14:32</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ยกเลิกคำขอจอง</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>BK801 (รถแทรกเตอร์ คูโบต้า 50 แรงม้า) เหตุผล: ฝนตกหนัก น้ำท่วมแปลงนาไม่สามารถลงแปลงได้</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:14:32</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>แก้ไขคำขอจอง</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BK802 เปลี่ยนเป็น รถขุดมันสำปะหลัง (กข 1111) (2026-10-29 10:00 - 2026-10-29 16:00) เหตุผล: ขอเปลี่ยนเป็นรถขุดมันสำปะหลังเนื่องจากเก็บเกี่ยวข้าวเสร็จแล้ว</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:14:32</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>แก้ไขคำขอจอง</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>BK802 เปลี่ยนเป็น รถขุดมันสำปะหลัง (กข 1111) (2026-10-29 10:30 - 2026-10-29 16:30) เหตุผล: ขอขยับเวลาเริ่มใช้งานครึ่งชั่วโมงครับ</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:31:20</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>พยายามยกเลิกรายการจองของผู้อื่น</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>BK803 โดย นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:31:20</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>พยายามแก้ไขรายการจองของผู้อื่น</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>BK803 โดย นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:31:20</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ยกเลิกคำขอจอง</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BK801 (รถแทรกเตอร์ คูโบต้า 50 แรงม้า) เหตุผล: ฝนตกหนัก น้ำท่วมแปลงนาไม่สามารถลงแปลงได้</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:31:20</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>แก้ไขคำขอจอง</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>BK802 เปลี่ยนเป็น รถขุดมันสำปะหลัง (กข 1111) (2026-10-29 10:00 - 2026-10-29 16:00) เหตุผล: ขอเปลี่ยนเป็นรถขุดมันสำปะหลังเนื่องจากเก็บเกี่ยวข้าวเสร็จแล้ว</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:31:21</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>แก้ไขคำขอจอง</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>BK802 เปลี่ยนเป็น รถขุดมันสำปะหลัง (กข 1111) (2026-10-29 10:30 - 2026-10-29 16:30) เหตุผล: ขอขยับเวลาเริ่มใช้งานครึ่งชั่วโมงครับ</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:35:55</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>พยายามยกเลิกรายการจองของผู้อื่น</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>BK803 โดย นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:35:55</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>พยายามแก้ไขรายการจองของผู้อื่น</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>BK803 โดย นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:35:55</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ยกเลิกคำขอจอง</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>BK801 (รถแทรกเตอร์ คูโบต้า 50 แรงม้า) เหตุผล: ฝนตกหนัก น้ำท่วมแปลงนาไม่สามารถลงแปลงได้</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:35:55</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>แก้ไขคำขอจอง</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>BK802 เปลี่ยนเป็น รถขุดมันสำปะหลัง (กข 1111) (2026-10-29 10:00 - 2026-10-29 16:00) เหตุผล: ขอเปลี่ยนเป็นรถขุดมันสำปะหลังเนื่องจากเก็บเกี่ยวข้าวเสร็จแล้ว</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:35:55</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>แก้ไขคำขอจอง</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>BK802 เปลี่ยนเป็น รถขุดมันสำปะหลัง (กข 1111) (2026-10-29 10:30 - 2026-10-29 16:30) เหตุผล: ขอขยับเวลาเริ่มใช้งานครึ่งชั่วโมงครับ</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-10-27 19:23:56</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>สร้างคำขอจอง</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>BK026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>นายสมเกียรติ สุขเกษม</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>รหัสแจ้งเตือน</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>รหัสผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ชื่อผู้ใช้</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>อีเมล</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>รหัสคำสั่งจอง</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ยานพาหนะ</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>สถานะ</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>เหตุผล/หมายเหตุ</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>วันที่/เวลา</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>อ่านแล้ว</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>N0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>BK011</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>รถแทรกเตอร์การเกษตร (ฟห 1234)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>อนุมัติ</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:28:39</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>N0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>นางสมศรี สดใส</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>somsri@farm.go.th</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>BK012</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>รถเกี่ยวนวดข้าว (นข 1234)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ไม่อนุมัติ</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>รถคันนี้อยู่ในรอบการซ่อมบำรุงประจำเดือน</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:28:49</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>N0003</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>BK801</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>รถแทรกเตอร์ คูโบต้า 50 แรงม้า</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ยกเลิกแล้ว</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ยกเลิกคำขอจองเรียบร้อยแล้ว (เหตุผล: ไม่ไป)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:12:43</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>N0004</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BK801</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>รถแทรกเตอร์ คูโบต้า 50 แรงม้า</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ยกเลิกแล้ว</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ยกเลิกคำขอจองเรียบร้อยแล้ว (เหตุผล: ฝนตกหนัก น้ำท่วมแปลงนาไม่สามารถลงแปลงได้)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:12:57</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>N0005</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>BK801</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>รถแทรกเตอร์ คูโบต้า 50 แรงม้า</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ยกเลิกแล้ว</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ยกเลิกคำขอจองเรียบร้อยแล้ว (เหตุผล: ไม่ไป)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:13:19</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>N0006</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BK801</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>รถแทรกเตอร์ คูโบต้า 50 แรงม้า</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ยกเลิกแล้ว</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ยกเลิกคำขอจองเรียบร้อยแล้ว (เหตุผล: ไม่ไป)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:13:27</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>N0007</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>BK801</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>รถแทรกเตอร์ คูโบต้า 50 แรงม้า</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ยกเลิกแล้ว</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ยกเลิกคำขอจองเรียบร้อยแล้ว (เหตุผล: ฝนตกหนัก น้ำท่วมแปลงนาไม่สามารถลงแปลงได้)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:13:27</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>N0008</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>BK801</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>รถแทรกเตอร์ คูโบต้า 50 แรงม้า</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ยกเลิกแล้ว</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ยกเลิกคำขอจองเรียบร้อยแล้ว (เหตุผล: ไม่ไป)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:13:44</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>N0009</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BK801</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>รถแทรกเตอร์ คูโบต้า 50 แรงม้า</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ยกเลิกแล้ว</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ยกเลิกคำขอจองเรียบร้อยแล้ว (เหตุผล: ฝนตกหนัก น้ำท่วมแปลงนาไม่สามารถลงแปลงได้)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:14:32</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>N0010</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>BK802</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>รถขุดมันสำปะหลัง (กข 1111)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>แก้ไขข้อมูลสำเร็จ (ขอเปลี่ยนเป็นรถขุดมันสำปะหลังเนื่องจากเก็บเกี่ยวข้าวเสร็จแล้ว) (สถานะคำขอถูกปรับกลับเป็น 'รออนุมัติ' เพื่อให้เจ้าหน้าที่ตรวจสอบใหม่อีกครั้ง)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:14:32</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>N0011</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>BK802</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>รถขุดมันสำปะหลัง (กข 1111)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>แก้ไขข้อมูลสำเร็จ (ขอขยับเวลาเริ่มใช้งานครึ่งชั่วโมงครับ)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:14:32</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>N0003</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BK801</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>รถแทรกเตอร์ คูโบต้า 50 แรงม้า</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ยกเลิกแล้ว</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ยกเลิกคำขอจองเรียบร้อยแล้ว (เหตุผล: ฝนตกหนัก น้ำท่วมแปลงนาไม่สามารถลงแปลงได้)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:15:19</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>N0004</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BK802</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>รถขุดมันสำปะหลัง (กข 1111)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>แก้ไขข้อมูลสำเร็จ (ขอเปลี่ยนเป็นรถขุดมันสำปะหลังเนื่องจากเก็บเกี่ยวข้าวเสร็จแล้ว) (สถานะคำขอถูกปรับกลับเป็น 'รออนุมัติ' เพื่อให้เจ้าหน้าที่ตรวจสอบใหม่อีกครั้ง)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:15:29</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>N0005</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BK802</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>รถขุดมันสำปะหลัง (กข 1111)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>แก้ไขข้อมูลสำเร็จ (ขอขยับเวลาเริ่มใช้งานครึ่งชั่วโมงครับ)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:15:33</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>N0015</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BK801</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>รถแทรกเตอร์ คูโบต้า 50 แรงม้า</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ยกเลิกแล้ว</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ยกเลิกคำขอจองเรียบร้อยแล้ว (เหตุผล: ฝนตกหนัก น้ำท่วมแปลงนาไม่สามารถลงแปลงได้)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:31:20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>N0016</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BK802</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>รถขุดมันสำปะหลัง (กข 1111)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>แก้ไขข้อมูลสำเร็จ (ขอเปลี่ยนเป็นรถขุดมันสำปะหลังเนื่องจากเก็บเกี่ยวข้าวเสร็จแล้ว) (สถานะคำขอถูกปรับกลับเป็น 'รออนุมัติ' เพื่อให้เจ้าหน้าที่ตรวจสอบใหม่อีกครั้ง)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:31:20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>N0017</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>BK802</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>รถขุดมันสำปะหลัง (กข 1111)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>แก้ไขข้อมูลสำเร็จ (ขอขยับเวลาเริ่มใช้งานครึ่งชั่วโมงครับ)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:31:21</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>N0018</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>BK801</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>รถแทรกเตอร์ คูโบต้า 50 แรงม้า</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ยกเลิกแล้ว</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ยกเลิกคำขอจองเรียบร้อยแล้ว (เหตุผล: ฝนตกหนัก น้ำท่วมแปลงนาไม่สามารถลงแปลงได้)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:35:55</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>N0019</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>BK802</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>รถขุดมันสำปะหลัง (กข 1111)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>แก้ไขข้อมูลสำเร็จ (ขอเปลี่ยนเป็นรถขุดมันสำปะหลังเนื่องจากเก็บเกี่ยวข้าวเสร็จแล้ว) (สถานะคำขอถูกปรับกลับเป็น 'รออนุมัติ' เพื่อให้เจ้าหน้าที่ตรวจสอบใหม่อีกครั้ง)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:35:55</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>N0020</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>นายทดสอบ ยกเลิกแก้ไข</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>BK802</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>รถขุดมันสำปะหลัง (กข 1111)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>รออนุมัติ</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>แก้ไขข้อมูลสำเร็จ (ขอขยับเวลาเริ่มใช้งานครึ่งชั่วโมงครับ)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:35:55</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>N0006</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>นางสมศรี สดใส</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>somsri@farm.go.th</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>BK016</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>รถคีบอ้อย / รถตักการเกษตร (ตอ 4455)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>อนุมัติ</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-10-27 19:50:06</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>

--- a/CarBooking.xlsx
+++ b/CarBooking.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>User@123</t>
+          <t>NewPass#999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2099-12-31</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1561,14 +1561,14 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>รออนุมัติ</t>
+          <t>อนุมัติ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BK001</t>
+          <t>BK015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1625,7 +1625,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BK001</t>
+          <t>BK016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1682,7 +1682,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BK002</t>
+          <t>BK017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1910,7 +1910,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BK011</t>
+          <t>BK021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BK012</t>
+          <t>BK022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2024,7 +2024,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BK013</t>
+          <t>BK023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2081,7 +2081,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BK014</t>
+          <t>BK024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2099-12-31</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2138,7 +2138,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BK015</t>
+          <t>BK025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2252,7 +2252,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BK016</t>
+          <t>BK027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2722,7 +2722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4812,6 +4812,556 @@
       <c r="D95" t="inlineStr">
         <is>
           <t>นายสมเกียรติ สุขเกษม</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:01:40</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ตั้งรหัสผ่านใหม่</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ผู้ใช้ U001 (นายสมชาย ใจดี)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:01:40</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:01:40</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>พยายามแก้ไขรายการจองของผู้อื่น</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>BK014 โดย นายสมชาย ใจดี</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:01:48</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ตั้งรหัสผ่านใหม่</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ผู้ใช้ U001 (นายสมชาย ใจดี)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:01:48</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:01:48</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>พยายามแก้ไขรายการจองของผู้อื่น</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>BK014 โดย นายสมชาย ใจดี</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:01:57</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ตั้งรหัสผ่านใหม่</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ผู้ใช้ U001 (นายสมชาย ใจดี)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:01:57</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:01:57</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>พยายามแก้ไขรายการจองของผู้อื่น</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>BK014 โดย นายสมชาย ใจดี</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:02:03</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ตั้งรหัสผ่านใหม่</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>ผู้ใช้ U001 (นายสมชาย ใจดี)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:02:03</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:02:03</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>พยายามแก้ไขรายการจองของผู้อื่น</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>BK014 โดย นายสมชาย ใจดี</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:02:36</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ตั้งรหัสผ่านใหม่</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ผู้ใช้ U001 (นายสมชาย ใจดี)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:02:36</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:02:36</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>พยายามแก้ไขรายการจองของผู้อื่น</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>BK014 โดย นายสมชาย ใจดี</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:02:45</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ตั้งรหัสผ่านใหม่</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ผู้ใช้ U001 (นายสมชาย ใจดี)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:02:45</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:02:45</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>พยายามแก้ไขรายการจองของผู้อื่น</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>BK014 โดย นายสมชาย ใจดี</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:02:55</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>ตั้งรหัสผ่านใหม่</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ผู้ใช้ U001 (นายสมชาย ใจดี)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:02:55</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:02:55</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>พยายามแก้ไขรายการจองของผู้อื่น</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>BK014 โดย นายสมชาย ใจดี</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:06:54</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>ตั้งรหัสผ่านใหม่</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ผู้ใช้ U001 (นายสมชาย ใจดี)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:06:54</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:07:18</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>ตั้งรหัสผ่านใหม่</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ผู้ใช้ U001 (นายสมชาย ใจดี)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:07:18</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
         </is>
       </c>
     </row>

--- a/CarBooking.xlsx
+++ b/CarBooking.xlsx
@@ -2722,7 +2722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5360,6 +5360,94 @@
         </is>
       </c>
       <c r="D120" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:25:44</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ตั้งรหัสผ่านใหม่</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ผู้ใช้ U001 (นายสมชาย ใจดี)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:25:44</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:26:18</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>ตั้งรหัสผ่านใหม่</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ผู้ใช้ U001 (นายสมชาย ใจดี)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:26:18</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
         <is>
           <t>นายสมชาย ใจดี</t>
         </is>

--- a/CarBooking.xlsx
+++ b/CarBooking.xlsx
@@ -2722,7 +2722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D124"/>
+  <dimension ref="A1:D136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5448,6 +5448,270 @@
         </is>
       </c>
       <c r="D124" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:39:18</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>ตั้งรหัสผ่านใหม่</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ผู้ใช้ U001 (นายสมชาย ใจดี)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:39:18</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:40:00</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ตั้งรหัสผ่านใหม่</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ผู้ใช้ U001 (นายสมชาย ใจดี)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:40:00</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:56:46</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>ตั้งรหัสผ่านใหม่</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ผู้ใช้ U001 (นายสมชาย ใจดี)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:56:46</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:57:06</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>ตั้งรหัสผ่านใหม่</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ผู้ใช้ U001 (นายสมชาย ใจดี)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:57:06</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:58:08</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>ตั้งรหัสผ่านใหม่</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ผู้ใช้ U001 (นายสมชาย ใจดี)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:58:08</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:18:56</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>ตั้งรหัสผ่านใหม่</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ผู้ใช้ U001 (นายสมชาย ใจดี)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:18:56</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>เข้าสู่ระบบผู้ใช้</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
         <is>
           <t>นายสมชาย ใจดี</t>
         </is>
@@ -5464,7 +5728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6431,6 +6695,110 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>N0022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>BK999_TEST</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>รถเกี่ยวนวดข้าว (นข 1234)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ไม่อนุมัติ</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ยานพาหนะอยู่ระหว่างการซ่อมบำรุงประจำปี</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:18:50</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>N0023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>นายสมชาย ใจดี</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>somchai@farm.go.th</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>BK999_TEST</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>รถเกี่ยวนวดข้าว (นข 1234)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ไม่อนุมัติ</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ยานพาหนะอยู่ระหว่างการซ่อมบำรุงประจำปี</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:18:56</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
